--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.99210968639488</v>
+        <v>3.086217824039168</v>
       </c>
       <c r="D2" t="n">
-        <v>18.76743477269956</v>
+        <v>3.049708150563678</v>
       </c>
       <c r="E2" t="n">
-        <v>16.33417510454644</v>
+        <v>2.654303454488796</v>
       </c>
       <c r="F2" t="n">
-        <v>16.72025377910921</v>
+        <v>2.717041239105247</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.05422823330004</v>
+        <v>1.633812087911257</v>
       </c>
       <c r="D3" t="n">
-        <v>9.970423057958028</v>
+        <v>1.62019374691818</v>
       </c>
       <c r="E3" t="n">
-        <v>16.33417510454644</v>
+        <v>2.654303454488796</v>
       </c>
       <c r="F3" t="n">
-        <v>16.72025377910921</v>
+        <v>2.717041239105247</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.29755940445427</v>
+        <v>7.848353403223819</v>
       </c>
       <c r="D4" t="n">
-        <v>49.01009557637236</v>
+        <v>7.96414053116051</v>
       </c>
       <c r="E4" t="n">
-        <v>16.33417510454644</v>
+        <v>2.654303454488796</v>
       </c>
       <c r="F4" t="n">
-        <v>16.72025377910921</v>
+        <v>2.717041239105247</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
